--- a/salidas/empresas/EMR.xlsx
+++ b/salidas/empresas/EMR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.18003845214844</v>
+        <v>22.1800422668457</v>
       </c>
       <c r="C2" t="n">
         <v>38.72499847412109</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.55295944213867</v>
+        <v>23.5529727935791</v>
       </c>
       <c r="C3" t="n">
         <v>40.90499877929688</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.07694435119629</v>
+        <v>24.07694816589355</v>
       </c>
       <c r="C4" t="n">
         <v>41.81499862670898</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>24.45695877075195</v>
+        <v>24.45696830749512</v>
       </c>
       <c r="C5" t="n">
         <v>42.47499847412109</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>23.87898826599121</v>
+        <v>23.87897300720215</v>
       </c>
       <c r="C6" t="n">
         <v>41.2599983215332</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25227355957031</v>
+        <v>24.25228500366211</v>
       </c>
       <c r="C7" t="n">
         <v>41.90499877929688</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>22.83724212646484</v>
+        <v>22.83725929260254</v>
       </c>
       <c r="C8" t="n">
         <v>39.45999908447266</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>23.90592193603516</v>
+        <v>23.90591812133789</v>
       </c>
       <c r="C9" t="n">
         <v>41.07500076293945</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>24.56068229675293</v>
+        <v>24.56067657470703</v>
       </c>
       <c r="C11" t="n">
         <v>42.20000076293945</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>25.38202095031738</v>
+        <v>25.38201141357422</v>
       </c>
       <c r="C12" t="n">
         <v>43.34999847412109</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>26.33055114746094</v>
+        <v>26.33053779602051</v>
       </c>
       <c r="C14" t="n">
         <v>44.97000122070312</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.35577392578125</v>
+        <v>25.35577774047852</v>
       </c>
       <c r="C15" t="n">
         <v>43.04999923706055</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>25.37933921813965</v>
+        <v>25.37934684753418</v>
       </c>
       <c r="C16" t="n">
         <v>43.09000015258789</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.69793701171875</v>
+        <v>28.69794654846191</v>
       </c>
       <c r="C18" t="n">
         <v>48.45000076293945</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>27.72061538696289</v>
+        <v>27.72061729431152</v>
       </c>
       <c r="C19" t="n">
         <v>46.79999923706055</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>27.88055229187012</v>
+        <v>27.88054084777832</v>
       </c>
       <c r="C20" t="n">
         <v>47.06999969482422</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>29.3240966796875</v>
+        <v>29.32408332824707</v>
       </c>
       <c r="C21" t="n">
         <v>49.22999954223633</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>31.70073127746582</v>
+        <v>31.70075416564941</v>
       </c>
       <c r="C22" t="n">
         <v>53.22000122070312</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>31.13487243652344</v>
+        <v>31.13488578796387</v>
       </c>
       <c r="C23" t="n">
         <v>52.27000045776367</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>34.14848709106445</v>
+        <v>34.14849853515625</v>
       </c>
       <c r="C24" t="n">
         <v>57.02000045776367</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>33.93290710449219</v>
+        <v>33.93289184570312</v>
       </c>
       <c r="C25" t="n">
         <v>56.65999984741211</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.41142845153809</v>
+        <v>30.41142463684082</v>
       </c>
       <c r="C26" t="n">
         <v>50.77999877929688</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.99929618835449</v>
+        <v>30.99930000305176</v>
       </c>
       <c r="C28" t="n">
         <v>51.45999908447266</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.4812126159668</v>
+        <v>31.48121643066406</v>
       </c>
       <c r="C29" t="n">
         <v>52.2599983215332</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>35.23491287231445</v>
+        <v>35.23492050170898</v>
       </c>
       <c r="C30" t="n">
         <v>58.18000030517578</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>29.94786643981934</v>
+        <v>29.94785499572754</v>
       </c>
       <c r="C31" t="n">
         <v>49.45000076293945</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>29.49363899230957</v>
+        <v>29.49364852905273</v>
       </c>
       <c r="C32" t="n">
         <v>48.70000076293945</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.51703071594238</v>
+        <v>28.51703453063965</v>
       </c>
       <c r="C33" t="n">
         <v>46.79999923706055</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.85490798950195</v>
+        <v>24.85491180419922</v>
       </c>
       <c r="C34" t="n">
         <v>40.79000091552734</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>19.94363594055176</v>
+        <v>19.94364547729492</v>
       </c>
       <c r="C35" t="n">
         <v>32.72999954223633</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>22.09854698181152</v>
+        <v>22.09854125976562</v>
       </c>
       <c r="C36" t="n">
         <v>35.88999938964844</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>20.13437461853027</v>
+        <v>20.13437080383301</v>
       </c>
       <c r="C38" t="n">
         <v>32.70000076293945</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>16.63821792602539</v>
+        <v>16.63822174072266</v>
       </c>
       <c r="C39" t="n">
         <v>26.75</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>17.77646255493164</v>
+        <v>17.77646446228027</v>
       </c>
       <c r="C40" t="n">
         <v>28.57999992370605</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.17252540588379</v>
+        <v>21.17253112792969</v>
       </c>
       <c r="C41" t="n">
         <v>34.04000091552734</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.14723968505859</v>
+        <v>20.14724349975586</v>
       </c>
       <c r="C42" t="n">
         <v>32.09000015258789</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>20.34188079833984</v>
+        <v>20.34187698364258</v>
       </c>
       <c r="C43" t="n">
         <v>32.40000152587891</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.39665031433105</v>
+        <v>25.39664840698242</v>
       </c>
       <c r="C46" t="n">
         <v>40.08000183105469</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>23.92025184631348</v>
+        <v>23.92024803161621</v>
       </c>
       <c r="C47" t="n">
         <v>37.75</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>26.45108795166016</v>
+        <v>26.45108413696289</v>
       </c>
       <c r="C48" t="n">
         <v>41.40999984741211</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.21121788024902</v>
+        <v>27.21121978759766</v>
       </c>
       <c r="C49" t="n">
         <v>42.59999847412109</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>26.53412818908691</v>
+        <v>26.53413581848145</v>
       </c>
       <c r="C50" t="n">
         <v>41.54000091552734</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>30.46170043945312</v>
+        <v>30.46170425415039</v>
       </c>
       <c r="C51" t="n">
         <v>47.34000015258789</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.3921012878418</v>
+        <v>32.39212036132812</v>
       </c>
       <c r="C52" t="n">
         <v>50.34000015258789</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>33.60826110839844</v>
+        <v>33.60824203491211</v>
       </c>
       <c r="C53" t="n">
         <v>52.22999954223633</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>30.08455276489258</v>
+        <v>30.08454704284668</v>
       </c>
       <c r="C54" t="n">
         <v>46.43999862670898</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.30305671691895</v>
+        <v>28.30305862426758</v>
       </c>
       <c r="C55" t="n">
         <v>43.68999862670898</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>30.42141914367676</v>
+        <v>30.4213981628418</v>
       </c>
       <c r="C57" t="n">
         <v>46.65000152587891</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>34.34065246582031</v>
+        <v>34.34065628051758</v>
       </c>
       <c r="C58" t="n">
         <v>52.65999984741211</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>35.80139541625977</v>
+        <v>35.80139923095703</v>
       </c>
       <c r="C59" t="n">
         <v>54.90000152587891</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>36.13147735595703</v>
+        <v>36.1314811706543</v>
       </c>
       <c r="C60" t="n">
         <v>55.06999969482422</v>
@@ -1703,11 +1715,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>37.50929260253906</v>
+        <v>37.50930786132812</v>
       </c>
       <c r="C61" t="n">
         <v>57.16999816894531</v>
@@ -1732,11 +1744,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>38.63123321533203</v>
+        <v>38.6312370300293</v>
       </c>
       <c r="C62" t="n">
         <v>58.88000106811523</v>
@@ -1761,11 +1773,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.36442184448242</v>
+        <v>39.36442947387695</v>
       </c>
       <c r="C63" t="n">
         <v>59.65999984741211</v>
@@ -1790,11 +1802,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>38.55287170410156</v>
+        <v>38.55286407470703</v>
       </c>
       <c r="C64" t="n">
         <v>58.43000030517578</v>
@@ -1819,11 +1831,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>40.09681701660156</v>
+        <v>40.09682464599609</v>
       </c>
       <c r="C65" t="n">
         <v>60.77000045776367</v>
@@ -1848,11 +1860,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>36.21846389770508</v>
+        <v>36.21845245361328</v>
       </c>
       <c r="C66" t="n">
         <v>54.54999923706055</v>
@@ -1877,11 +1889,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.34716796875</v>
+        <v>37.34716033935547</v>
       </c>
       <c r="C67" t="n">
         <v>56.25</v>
@@ -1906,11 +1918,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>32.59328842163086</v>
+        <v>32.59329223632812</v>
       </c>
       <c r="C68" t="n">
         <v>49.09000015258789</v>
@@ -1935,11 +1947,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.14709281921387</v>
+        <v>31.14708709716797</v>
       </c>
       <c r="C69" t="n">
         <v>46.54999923706055</v>
@@ -1964,11 +1976,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>27.64095115661621</v>
+        <v>27.64095306396484</v>
       </c>
       <c r="C70" t="n">
         <v>41.31000137329102</v>
@@ -1993,11 +2005,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.19760513305664</v>
+        <v>32.19758987426758</v>
       </c>
       <c r="C71" t="n">
         <v>48.11999893188477</v>
@@ -2022,11 +2034,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>35.23801040649414</v>
+        <v>35.23799514770508</v>
       </c>
       <c r="C72" t="n">
         <v>52.25</v>
@@ -2051,11 +2063,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>31.42082595825195</v>
+        <v>31.42082786560059</v>
       </c>
       <c r="C73" t="n">
         <v>46.59000015258789</v>
@@ -2080,11 +2092,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>34.65126419067383</v>
+        <v>34.65126037597656</v>
       </c>
       <c r="C74" t="n">
         <v>51.38000106811523</v>
@@ -2109,11 +2121,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>34.19461822509766</v>
+        <v>34.19462203979492</v>
       </c>
       <c r="C75" t="n">
         <v>50.31000137329102</v>
@@ -2138,11 +2150,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.46561050415039</v>
+        <v>35.46561813354492</v>
       </c>
       <c r="C76" t="n">
         <v>52.18000030517578</v>
@@ -2167,11 +2179,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>35.71030044555664</v>
+        <v>35.71029663085938</v>
       </c>
       <c r="C77" t="n">
         <v>52.54000091552734</v>
@@ -2196,11 +2208,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.04932403564453</v>
+        <v>32.04933166503906</v>
       </c>
       <c r="C78" t="n">
         <v>46.77000045776367</v>
@@ -2225,11 +2237,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>31.91913223266602</v>
+        <v>31.91912651062012</v>
       </c>
       <c r="C79" t="n">
         <v>46.58000183105469</v>
@@ -2254,11 +2266,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>32.73456954956055</v>
+        <v>32.73458099365234</v>
       </c>
       <c r="C80" t="n">
         <v>47.77000045776367</v>
@@ -2283,11 +2295,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>35.02651214599609</v>
+        <v>35.02650451660156</v>
       </c>
       <c r="C81" t="n">
         <v>50.72000122070312</v>
@@ -2312,11 +2324,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.33456420898438</v>
+        <v>33.33457183837891</v>
       </c>
       <c r="C82" t="n">
         <v>48.27000045776367</v>
@@ -2341,11 +2353,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>33.445068359375</v>
+        <v>33.44505310058594</v>
       </c>
       <c r="C83" t="n">
         <v>48.43000030517578</v>
@@ -2370,11 +2382,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>34.97542953491211</v>
+        <v>34.97543334960938</v>
       </c>
       <c r="C84" t="n">
         <v>50.22999954223633</v>
@@ -2399,11 +2411,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>36.87633895874023</v>
+        <v>36.87634658813477</v>
       </c>
       <c r="C85" t="n">
         <v>52.95999908447266</v>
@@ -2428,11 +2440,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>39.86349868774414</v>
+        <v>39.86348724365234</v>
       </c>
       <c r="C86" t="n">
         <v>57.25</v>
@@ -2457,11 +2469,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>39.76121520996094</v>
+        <v>39.76120376586914</v>
       </c>
       <c r="C87" t="n">
         <v>56.70000076293945</v>
@@ -2486,11 +2498,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>39.17916870117188</v>
+        <v>39.17917251586914</v>
       </c>
       <c r="C88" t="n">
         <v>55.86999893188477</v>
@@ -2515,11 +2527,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>38.92671203613281</v>
+        <v>38.92671966552734</v>
       </c>
       <c r="C89" t="n">
         <v>55.5099983215332</v>
@@ -2544,7 +2556,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2573,11 +2585,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>38.51414108276367</v>
+        <v>38.51414489746094</v>
       </c>
       <c r="C91" t="n">
         <v>54.54000091552734</v>
@@ -2602,11 +2614,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>43.33723831176758</v>
+        <v>43.33723068237305</v>
       </c>
       <c r="C92" t="n">
         <v>61.36999893188477</v>
@@ -2631,11 +2643,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>42.91298675537109</v>
+        <v>42.9129753112793</v>
       </c>
       <c r="C93" t="n">
         <v>60.36999893188477</v>
@@ -2660,11 +2672,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>45.99088287353516</v>
+        <v>45.99089050292969</v>
       </c>
       <c r="C94" t="n">
         <v>64.69999694824219</v>
@@ -2689,11 +2701,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>47.6044807434082</v>
+        <v>47.60446548461914</v>
       </c>
       <c r="C95" t="n">
         <v>66.97000122070312</v>
@@ -2718,11 +2730,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>47.9295539855957</v>
+        <v>47.92956161499023</v>
       </c>
       <c r="C96" t="n">
         <v>66.98999786376953</v>
@@ -2747,11 +2759,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>50.21191787719727</v>
+        <v>50.2119140625</v>
       </c>
       <c r="C97" t="n">
         <v>70.18000030517578</v>
@@ -2776,7 +2788,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2805,7 +2817,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2834,11 +2846,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>48.11213684082031</v>
+        <v>48.11214828491211</v>
       </c>
       <c r="C100" t="n">
         <v>66.80000305175781</v>
@@ -2863,11 +2875,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>49.10608291625977</v>
+        <v>49.1060791015625</v>
       </c>
       <c r="C101" t="n">
         <v>68.18000030517578</v>
@@ -2892,11 +2904,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.3663215637207</v>
+        <v>48.36631393432617</v>
       </c>
       <c r="C102" t="n">
         <v>66.73000335693359</v>
@@ -2921,11 +2933,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>48.09813690185547</v>
+        <v>48.09814834594727</v>
       </c>
       <c r="C103" t="n">
         <v>66.36000061035156</v>
@@ -2950,11 +2962,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>46.13390731811523</v>
+        <v>46.13391876220703</v>
       </c>
       <c r="C104" t="n">
         <v>63.65000152587891</v>
@@ -2979,11 +2991,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>46.72265625</v>
+        <v>46.72267532348633</v>
       </c>
       <c r="C105" t="n">
         <v>64.01999664306641</v>
@@ -3008,7 +3020,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3037,11 +3049,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>46.75185775756836</v>
+        <v>46.75186157226562</v>
       </c>
       <c r="C107" t="n">
         <v>64.05999755859375</v>
@@ -3066,11 +3078,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>46.86681365966797</v>
+        <v>46.8668098449707</v>
       </c>
       <c r="C108" t="n">
         <v>63.75</v>
@@ -3095,11 +3107,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>45.38176345825195</v>
+        <v>45.38177871704102</v>
       </c>
       <c r="C109" t="n">
         <v>61.72999954223633</v>
@@ -3124,11 +3136,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>41.86034774780273</v>
+        <v>41.86033630371094</v>
       </c>
       <c r="C110" t="n">
         <v>56.93999862670898</v>
@@ -3153,11 +3165,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>42.92842102050781</v>
+        <v>42.92844009399414</v>
       </c>
       <c r="C111" t="n">
         <v>57.91999816894531</v>
@@ -3182,11 +3194,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.96490859985352</v>
+        <v>41.96491241455078</v>
       </c>
       <c r="C112" t="n">
         <v>56.61999893188477</v>
@@ -3211,7 +3223,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3240,11 +3252,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>45.05165481567383</v>
+        <v>45.05166244506836</v>
       </c>
       <c r="C114" t="n">
         <v>60.31000137329102</v>
@@ -3269,11 +3281,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>41.40629959106445</v>
+        <v>41.40629577636719</v>
       </c>
       <c r="C115" t="n">
         <v>55.43000030517578</v>
@@ -3298,7 +3310,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3327,11 +3339,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>35.99264144897461</v>
+        <v>35.99264907836914</v>
       </c>
       <c r="C117" t="n">
         <v>47.72000122070312</v>
@@ -3356,11 +3368,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>33.31508636474609</v>
+        <v>33.31506729125977</v>
       </c>
       <c r="C118" t="n">
         <v>44.16999816894531</v>
@@ -3385,11 +3397,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>35.62306594848633</v>
+        <v>35.62305450439453</v>
       </c>
       <c r="C119" t="n">
         <v>47.22999954223633</v>
@@ -3414,11 +3426,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>38.08672332763672</v>
+        <v>38.08672714233398</v>
       </c>
       <c r="C120" t="n">
         <v>50</v>
@@ -3443,11 +3455,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>36.43377304077148</v>
+        <v>36.43376922607422</v>
       </c>
       <c r="C121" t="n">
         <v>47.83000183105469</v>
@@ -3472,11 +3484,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>35.02454376220703</v>
+        <v>35.02455902099609</v>
       </c>
       <c r="C122" t="n">
         <v>45.97999954223633</v>
@@ -3501,11 +3513,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>37.57598114013672</v>
+        <v>37.57598495483398</v>
       </c>
       <c r="C123" t="n">
         <v>48.83000183105469</v>
@@ -3530,11 +3542,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>41.84687042236328</v>
+        <v>41.84684753417969</v>
       </c>
       <c r="C124" t="n">
         <v>54.38000106811523</v>
@@ -3559,7 +3571,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3588,11 +3600,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>40.38938140869141</v>
+        <v>40.38937377929688</v>
       </c>
       <c r="C126" t="n">
         <v>52.02000045776367</v>
@@ -3617,11 +3629,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.49806976318359</v>
+        <v>40.49808502197266</v>
       </c>
       <c r="C127" t="n">
         <v>52.15999984741211</v>
@@ -3646,11 +3658,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>43.40188980102539</v>
+        <v>43.40188598632812</v>
       </c>
       <c r="C128" t="n">
         <v>55.90000152587891</v>
@@ -3675,11 +3687,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>41.26255798339844</v>
+        <v>41.2625732421875</v>
       </c>
       <c r="C129" t="n">
         <v>52.68000030517578</v>
@@ -3704,11 +3716,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>42.69594955444336</v>
+        <v>42.69595336914062</v>
       </c>
       <c r="C130" t="n">
         <v>54.5099983215332</v>
@@ -3733,11 +3745,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>39.6960334777832</v>
+        <v>39.69602966308594</v>
       </c>
       <c r="C131" t="n">
         <v>50.68000030517578</v>
@@ -3762,11 +3774,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>44.6328125</v>
+        <v>44.63281631469727</v>
       </c>
       <c r="C132" t="n">
         <v>56.43999862670898</v>
@@ -3791,11 +3803,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.08715057373047</v>
+        <v>44.0871696472168</v>
       </c>
       <c r="C133" t="n">
         <v>55.75</v>
@@ -3820,11 +3832,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>46.38840484619141</v>
+        <v>46.38839340209961</v>
       </c>
       <c r="C134" t="n">
         <v>58.65999984741211</v>
@@ -3849,11 +3861,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>47.88550567626953</v>
+        <v>47.8855094909668</v>
       </c>
       <c r="C135" t="n">
         <v>60.09999847412109</v>
@@ -3878,11 +3890,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>47.69427871704102</v>
+        <v>47.69427108764648</v>
       </c>
       <c r="C136" t="n">
         <v>59.86000061035156</v>
@@ -3907,11 +3919,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.02892684936523</v>
+        <v>48.0289192199707</v>
       </c>
       <c r="C137" t="n">
         <v>60.27999877929688</v>
@@ -3936,11 +3948,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>47.49205017089844</v>
+        <v>47.49203872680664</v>
       </c>
       <c r="C138" t="n">
         <v>59.11999893188477</v>
@@ -3965,11 +3977,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>47.89369583129883</v>
+        <v>47.8936882019043</v>
       </c>
       <c r="C139" t="n">
         <v>59.61999893188477</v>
@@ -3994,11 +4006,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>47.88566207885742</v>
+        <v>47.88566589355469</v>
       </c>
       <c r="C140" t="n">
         <v>59.61000061035156</v>
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4052,7 +4064,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4081,11 +4093,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>52.19634628295898</v>
+        <v>52.19633102416992</v>
       </c>
       <c r="C143" t="n">
         <v>64.45999908447266</v>
@@ -4110,11 +4122,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>52.91855621337891</v>
+        <v>52.91856002807617</v>
       </c>
       <c r="C144" t="n">
         <v>64.81999969482422</v>
@@ -4139,11 +4151,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>56.89438629150391</v>
+        <v>56.89437866210938</v>
       </c>
       <c r="C145" t="n">
         <v>69.69000244140625</v>
@@ -4168,11 +4180,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>58.968017578125</v>
+        <v>58.96801376342773</v>
       </c>
       <c r="C146" t="n">
         <v>72.23000335693359</v>
@@ -4197,11 +4209,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>58.41007995605469</v>
+        <v>58.41011428833008</v>
       </c>
       <c r="C147" t="n">
         <v>71.05999755859375</v>
@@ -4226,7 +4238,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4255,11 +4267,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>54.58788299560547</v>
+        <v>54.58787536621094</v>
       </c>
       <c r="C149" t="n">
         <v>66.41000366210938</v>
@@ -4284,11 +4296,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>58.62453842163086</v>
+        <v>58.62452697753906</v>
       </c>
       <c r="C150" t="n">
         <v>70.83999633789062</v>
@@ -4313,11 +4325,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>57.21770858764648</v>
+        <v>57.21768188476562</v>
       </c>
       <c r="C151" t="n">
         <v>69.13999938964844</v>
@@ -4342,11 +4354,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>59.81624603271484</v>
+        <v>59.81624221801758</v>
       </c>
       <c r="C152" t="n">
         <v>72.27999877929688</v>
@@ -4371,11 +4383,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>63.92034149169922</v>
+        <v>63.92035675048828</v>
       </c>
       <c r="C153" t="n">
         <v>76.73000335693359</v>
@@ -4400,11 +4412,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>63.79538726806641</v>
+        <v>63.79540252685547</v>
       </c>
       <c r="C154" t="n">
         <v>76.58000183105469</v>
@@ -4429,11 +4441,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>56.54780197143555</v>
+        <v>56.54779052734375</v>
       </c>
       <c r="C155" t="n">
         <v>67.87999725341797</v>
@@ -4458,11 +4470,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>56.65980911254883</v>
+        <v>56.65981292724609</v>
       </c>
       <c r="C156" t="n">
         <v>67.51999664306641</v>
@@ -4487,11 +4499,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>50.13957977294922</v>
+        <v>50.13959503173828</v>
       </c>
       <c r="C157" t="n">
         <v>59.75</v>
@@ -4516,11 +4528,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>54.93956756591797</v>
+        <v>54.93955230712891</v>
       </c>
       <c r="C158" t="n">
         <v>65.47000122070312</v>
@@ -4545,11 +4557,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>57.60107040405273</v>
+        <v>57.60106658935547</v>
       </c>
       <c r="C159" t="n">
         <v>68.15000152587891</v>
@@ -4574,11 +4586,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>57.87155151367188</v>
+        <v>57.87154769897461</v>
       </c>
       <c r="C160" t="n">
         <v>68.47000122070312</v>
@@ -4603,7 +4615,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4632,11 +4644,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>51.29891586303711</v>
+        <v>51.29893112182617</v>
       </c>
       <c r="C162" t="n">
         <v>60.2400016784668</v>
@@ -4661,11 +4673,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>56.81713485717773</v>
+        <v>56.817138671875</v>
       </c>
       <c r="C163" t="n">
         <v>66.72000122070312</v>
@@ -4690,11 +4702,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>55.250244140625</v>
+        <v>55.25024032592773</v>
       </c>
       <c r="C164" t="n">
         <v>64.87999725341797</v>
@@ -4719,11 +4731,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>51.1843376159668</v>
+        <v>51.18433380126953</v>
       </c>
       <c r="C165" t="n">
         <v>59.59000015258789</v>
@@ -4748,11 +4760,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>57.42885208129883</v>
+        <v>57.4288330078125</v>
       </c>
       <c r="C166" t="n">
         <v>66.86000061035156</v>
@@ -4777,7 +4789,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4806,11 +4818,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>63.87548828125</v>
+        <v>63.87547302246094</v>
       </c>
       <c r="C168" t="n">
         <v>73.86000061035156</v>
@@ -4835,11 +4847,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>65.9510498046875</v>
+        <v>65.95105743408203</v>
       </c>
       <c r="C169" t="n">
         <v>76.26000213623047</v>
@@ -4864,11 +4876,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>61.94692993164062</v>
+        <v>61.94693756103516</v>
       </c>
       <c r="C170" t="n">
         <v>71.62999725341797</v>
@@ -4893,11 +4905,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>55.81362533569336</v>
+        <v>55.81361770629883</v>
       </c>
       <c r="C171" t="n">
         <v>64.11000061035156</v>
@@ -4922,11 +4934,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>41.48368453979492</v>
+        <v>41.48368835449219</v>
       </c>
       <c r="C172" t="n">
         <v>47.65000152587891</v>
@@ -4951,11 +4963,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>49.64982223510742</v>
+        <v>49.64984130859375</v>
       </c>
       <c r="C173" t="n">
         <v>57.02999877929688</v>
@@ -4980,11 +4992,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>53.64025115966797</v>
+        <v>53.6402587890625</v>
       </c>
       <c r="C174" t="n">
         <v>61.02000045776367</v>
@@ -5009,7 +5021,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5038,7 +5050,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5067,11 +5079,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>61.49662399291992</v>
+        <v>61.49663162231445</v>
       </c>
       <c r="C177" t="n">
         <v>69.47000122070312</v>
@@ -5096,11 +5108,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>58.04423522949219</v>
+        <v>58.04423904418945</v>
       </c>
       <c r="C178" t="n">
         <v>65.56999969482422</v>
@@ -5125,11 +5137,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>57.35376358032227</v>
+        <v>57.3537712097168</v>
       </c>
       <c r="C179" t="n">
         <v>64.79000091552734</v>
@@ -5154,7 +5166,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5183,11 +5195,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>71.62852478027344</v>
+        <v>71.62851715087891</v>
       </c>
       <c r="C181" t="n">
         <v>80.37000274658203</v>
@@ -5212,7 +5224,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5241,11 +5253,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>77.0142822265625</v>
+        <v>77.01429748535156</v>
       </c>
       <c r="C183" t="n">
         <v>85.90000152587891</v>
@@ -5270,11 +5282,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>80.88739013671875</v>
+        <v>80.88739776611328</v>
       </c>
       <c r="C184" t="n">
         <v>90.22000122070312</v>
@@ -5299,11 +5311,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>81.12949371337891</v>
+        <v>81.12947845458984</v>
       </c>
       <c r="C185" t="n">
         <v>90.48999786376953</v>
@@ -5328,11 +5340,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>86.25823211669922</v>
+        <v>86.25823974609375</v>
       </c>
       <c r="C186" t="n">
         <v>95.69000244140625</v>
@@ -5357,11 +5369,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>86.75399780273438</v>
+        <v>86.75403594970703</v>
       </c>
       <c r="C187" t="n">
         <v>96.23999786376953</v>
@@ -5386,11 +5398,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>90.94568634033203</v>
+        <v>90.94566345214844</v>
       </c>
       <c r="C188" t="n">
         <v>100.8899993896484</v>
@@ -5415,11 +5427,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>95.56407928466797</v>
+        <v>95.5640869140625</v>
       </c>
       <c r="C189" t="n">
         <v>105.5</v>
@@ -5444,11 +5456,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>85.32830810546875</v>
+        <v>85.32831573486328</v>
       </c>
       <c r="C190" t="n">
         <v>94.19999694824219</v>
@@ -5473,7 +5485,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5502,7 +5514,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5531,7 +5543,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5560,7 +5572,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5589,11 +5601,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>85.0609130859375</v>
+        <v>85.06090545654297</v>
       </c>
       <c r="C195" t="n">
         <v>92.91999816894531</v>
@@ -5618,11 +5630,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>89.75701904296875</v>
+        <v>89.75701141357422</v>
       </c>
       <c r="C196" t="n">
         <v>98.05000305175781</v>
@@ -5647,11 +5659,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>82.55263519287109</v>
+        <v>82.55264282226562</v>
       </c>
       <c r="C197" t="n">
         <v>90.18000030517578</v>
@@ -5676,11 +5688,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>81.66714477539062</v>
+        <v>81.66715240478516</v>
       </c>
       <c r="C198" t="n">
         <v>88.66000366210938</v>
@@ -5705,11 +5717,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>73.2664794921875</v>
+        <v>73.26647186279297</v>
       </c>
       <c r="C199" t="n">
         <v>79.54000091552734</v>
@@ -5734,11 +5746,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>82.9659423828125</v>
+        <v>82.96592712402344</v>
       </c>
       <c r="C200" t="n">
         <v>90.06999969482422</v>
@@ -5763,11 +5775,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>75.73851776123047</v>
+        <v>75.73851013183594</v>
       </c>
       <c r="C201" t="n">
         <v>81.73999786376953</v>
@@ -5792,7 +5804,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5821,7 +5833,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5850,11 +5862,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>89.2469482421875</v>
+        <v>89.24694061279297</v>
       </c>
       <c r="C204" t="n">
         <v>95.76999664306641</v>
@@ -5879,11 +5891,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>89.51718902587891</v>
+        <v>89.51718139648438</v>
       </c>
       <c r="C205" t="n">
         <v>96.05999755859375</v>
@@ -5908,7 +5920,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5937,11 +5949,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>77.54037475585938</v>
+        <v>77.54036712646484</v>
       </c>
       <c r="C207" t="n">
         <v>82.70999908447266</v>
@@ -5966,11 +5978,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>81.6934814453125</v>
+        <v>81.69349670410156</v>
       </c>
       <c r="C208" t="n">
         <v>87.13999938964844</v>
@@ -5995,11 +6007,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>78.05599212646484</v>
+        <v>78.05600738525391</v>
       </c>
       <c r="C209" t="n">
         <v>83.26000213623047</v>
@@ -6024,7 +6036,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6053,11 +6065,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>85.27798461914062</v>
+        <v>85.27797698974609</v>
       </c>
       <c r="C211" t="n">
         <v>90.38999938964844</v>
@@ -6082,11 +6094,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>86.18369293212891</v>
+        <v>86.18370819091797</v>
       </c>
       <c r="C212" t="n">
         <v>91.34999847412109</v>
@@ -6111,11 +6123,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>93.19808197021484</v>
+        <v>93.19806671142578</v>
       </c>
       <c r="C213" t="n">
         <v>98.25</v>
@@ -6140,11 +6152,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>91.60445404052734</v>
+        <v>91.60446166992188</v>
       </c>
       <c r="C214" t="n">
         <v>96.56999969482422</v>
@@ -6169,7 +6181,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6198,11 +6210,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>84.83284759521484</v>
+        <v>84.83283233642578</v>
       </c>
       <c r="C216" t="n">
         <v>88.90000152587891</v>
@@ -6227,11 +6239,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>92.87716674804688</v>
+        <v>92.87717437744141</v>
       </c>
       <c r="C217" t="n">
         <v>97.33000183105469</v>
@@ -6256,11 +6268,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>87.53336334228516</v>
+        <v>87.53337097167969</v>
       </c>
       <c r="C218" t="n">
         <v>91.73000335693359</v>
@@ -6285,11 +6297,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>102.4679718017578</v>
+        <v>102.4679794311523</v>
       </c>
       <c r="C219" t="n">
         <v>106.8499984741211</v>
@@ -6314,11 +6326,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>108.7685470581055</v>
+        <v>108.7685394287109</v>
       </c>
       <c r="C220" t="n">
         <v>113.4199981689453</v>
@@ -6343,11 +6355,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>103.3598327636719</v>
+        <v>103.3598480224609</v>
       </c>
       <c r="C221" t="n">
         <v>107.7799987792969</v>
@@ -6372,11 +6384,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>108.0542907714844</v>
+        <v>108.0542755126953</v>
       </c>
       <c r="C222" t="n">
         <v>112.1600036621094</v>
@@ -6401,7 +6413,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6430,11 +6442,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>112.8230819702148</v>
+        <v>112.8230667114258</v>
       </c>
       <c r="C224" t="n">
         <v>117.1100006103516</v>
@@ -6459,11 +6471,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>102.0457992553711</v>
+        <v>102.0457916259766</v>
       </c>
       <c r="C225" t="n">
         <v>105.3899993896484</v>
@@ -6488,11 +6500,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>105.899528503418</v>
+        <v>105.8995132446289</v>
       </c>
       <c r="C226" t="n">
         <v>109.370002746582</v>
@@ -6517,11 +6529,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>104.8344116210938</v>
+        <v>104.8344039916992</v>
       </c>
       <c r="C227" t="n">
         <v>108.2699966430664</v>
@@ -6546,11 +6558,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>128.9200439453125</v>
+        <v>128.9200744628906</v>
       </c>
       <c r="C228" t="n">
         <v>132.6000061035156</v>
@@ -6575,11 +6587,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>120.4906845092773</v>
+        <v>120.4906616210938</v>
       </c>
       <c r="C229" t="n">
         <v>123.9300003051758</v>
@@ -6604,11 +6616,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>126.3435974121094</v>
+        <v>126.3435821533203</v>
       </c>
       <c r="C230" t="n">
         <v>129.9499969482422</v>
@@ -6633,7 +6645,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6662,11 +6674,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>107.04833984375</v>
+        <v>107.0483322143555</v>
       </c>
       <c r="C232" t="n">
         <v>109.6399993896484</v>
@@ -6691,7 +6703,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6720,11 +6732,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>117.0721435546875</v>
+        <v>117.072151184082</v>
       </c>
       <c r="C234" t="n">
         <v>119.379997253418</v>
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6778,11 +6790,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>142.6970062255859</v>
+        <v>142.697021484375</v>
       </c>
       <c r="C236" t="n">
         <v>145.5099945068359</v>
@@ -6807,11 +6819,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>129.9588317871094</v>
+        <v>129.9588623046875</v>
       </c>
       <c r="C237" t="n">
         <v>132</v>
@@ -6836,7 +6848,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6865,11 +6877,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>137.4118041992188</v>
+        <v>137.4117889404297</v>
       </c>
       <c r="C239" t="n">
         <v>139.5700073242188</v>
@@ -6894,7 +6906,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6923,7 +6935,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6952,7 +6964,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6981,7 +6993,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7010,7 +7022,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7039,7 +7051,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7068,7 +7080,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7097,7 +7109,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7126,7 +7138,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7155,7 +7167,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7184,32 +7196,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>154.5899963378906</v>
+        <v>156.1399993896484</v>
       </c>
       <c r="C250" t="n">
-        <v>154.5899963378906</v>
+        <v>156.1399993896484</v>
       </c>
       <c r="D250" t="n">
-        <v>36940400</v>
+        <v>39012200</v>
       </c>
       <c r="E250" t="n">
         <v>4.567690941385435</v>
       </c>
       <c r="F250" t="n">
-        <v>33.84423296620888</v>
+        <v>34.18357358089759</v>
       </c>
       <c r="G250" t="n">
         <v>557800000</v>
       </c>
       <c r="H250" t="n">
-        <v>86230299957.27539</v>
+        <v>87094891659.5459</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06622517031193977</v>
+        <v>0.06993940480458946</v>
       </c>
     </row>
   </sheetData>
@@ -7241,75 +7253,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40212</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7471,13 +7483,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7504,7 +7516,7 @@
       <c r="I6" t="n">
         <v>2.266930275471201</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K6" t="n">
@@ -7517,13 +7529,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40212</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7550,7 +7562,7 @@
       <c r="I7" t="n">
         <v>2.226930275471201</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K7" t="n">
@@ -7563,13 +7575,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7596,7 +7608,7 @@
       <c r="I8" t="n">
         <v>2.266930275471201</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K8" t="n">
@@ -7609,13 +7621,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7642,7 +7654,7 @@
       <c r="I9" t="n">
         <v>2.529003655436886</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K9" t="n">
@@ -7655,13 +7667,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7688,7 +7700,7 @@
       <c r="I10" t="n">
         <v>2.851505348261591</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K10" t="n">
@@ -7701,13 +7713,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40576</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7734,7 +7746,7 @@
       <c r="I11" t="n">
         <v>2.92150534826159</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40576</v>
       </c>
       <c r="K11" t="n">
@@ -7747,13 +7759,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7780,7 +7792,7 @@
       <c r="I12" t="n">
         <v>3.121505348261591</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K12" t="n">
@@ -7793,13 +7805,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7826,7 +7838,7 @@
       <c r="I13" t="n">
         <v>3.249431968295905</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K13" t="n">
@@ -7839,13 +7851,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7872,7 +7884,7 @@
       <c r="I14" t="n">
         <v>3.27</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="K14" t="n">
@@ -7885,13 +7897,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7918,7 +7930,7 @@
       <c r="I15" t="n">
         <v>3.14</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="K15" t="n">
@@ -7931,13 +7943,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7964,7 +7976,7 @@
       <c r="I16" t="n">
         <v>3.15</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7977,13 +7989,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8010,7 +8022,7 @@
       <c r="I17" t="n">
         <v>3.29</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -8023,13 +8035,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8056,7 +8068,7 @@
       <c r="I18" t="n">
         <v>2.67</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="K18" t="n">
@@ -8069,13 +8081,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8102,7 +8114,7 @@
       <c r="I19" t="n">
         <v>2.79</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="K19" t="n">
@@ -8115,13 +8127,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8148,7 +8160,7 @@
       <c r="I20" t="n">
         <v>2.82</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K20" t="n">
@@ -8161,13 +8173,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="I21" t="n">
         <v>2.05</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K21" t="n">
@@ -8207,13 +8219,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41597</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8240,7 +8252,7 @@
       <c r="I22" t="n">
         <v>2.76</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41597</v>
       </c>
       <c r="K22" t="n">
@@ -8253,13 +8265,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8286,7 +8298,7 @@
       <c r="I23" t="n">
         <v>2.79</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="K23" t="n">
@@ -8299,13 +8311,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8332,7 +8344,7 @@
       <c r="I24" t="n">
         <v>2.79</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K24" t="n">
@@ -8345,13 +8357,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8378,7 +8390,7 @@
       <c r="I25" t="n">
         <v>3.55</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K25" t="n">
@@ -8391,13 +8403,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8424,7 +8436,7 @@
       <c r="I26" t="n">
         <v>3.03</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="K26" t="n">
@@ -8437,13 +8449,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42039</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8470,7 +8482,7 @@
       <c r="I27" t="n">
         <v>3.13</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42039</v>
       </c>
       <c r="K27" t="n">
@@ -8483,13 +8495,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8516,7 +8528,7 @@
       <c r="I28" t="n">
         <v>3.78</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K28" t="n">
@@ -8529,13 +8541,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8562,7 +8574,7 @@
       <c r="I29" t="n">
         <v>3.59</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8575,13 +8587,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42326</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8608,7 +8620,7 @@
       <c r="I30" t="n">
         <v>3.99</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42326</v>
       </c>
       <c r="K30" t="n">
@@ -8621,13 +8633,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8654,7 +8666,7 @@
       <c r="I31" t="n">
         <v>3.77</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="K31" t="n">
@@ -8667,13 +8679,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8700,7 +8712,7 @@
       <c r="I32" t="n">
         <v>2.92</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8713,13 +8725,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8746,7 +8758,7 @@
       <c r="I33" t="n">
         <v>2.82</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8759,13 +8771,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42690</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="I34" t="n">
         <v>2.52</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42690</v>
       </c>
       <c r="K34" t="n">
@@ -8805,13 +8817,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="I35" t="n">
         <v>2.47</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="K35" t="n">
@@ -8851,13 +8863,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8884,7 +8896,7 @@
       <c r="I36" t="n">
         <v>2.35</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K36" t="n">
@@ -8897,13 +8909,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8930,7 +8942,7 @@
       <c r="I37" t="n">
         <v>2.25</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8943,13 +8955,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8976,7 +8988,7 @@
       <c r="I38" t="n">
         <v>2.35</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="K38" t="n">
@@ -8989,13 +9001,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9022,7 +9034,7 @@
       <c r="I39" t="n">
         <v>2.48</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="K39" t="n">
@@ -9035,13 +9047,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9068,7 +9080,7 @@
       <c r="I40" t="n">
         <v>2.79</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9081,13 +9093,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9114,7 +9126,7 @@
       <c r="I41" t="n">
         <v>3.27</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K41" t="n">
@@ -9127,13 +9139,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43423</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9160,7 +9172,7 @@
       <c r="I42" t="n">
         <v>3.46</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43423</v>
       </c>
       <c r="K42" t="n">
@@ -9173,13 +9185,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9206,7 +9218,7 @@
       <c r="I43" t="n">
         <v>3.59</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="K43" t="n">
@@ -9219,13 +9231,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9252,7 +9264,7 @@
       <c r="I44" t="n">
         <v>3.67</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K44" t="n">
@@ -9265,13 +9277,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9298,7 +9310,7 @@
       <c r="I45" t="n">
         <v>3.52</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K45" t="n">
@@ -9311,13 +9323,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43787</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9344,7 +9356,7 @@
       <c r="I46" t="n">
         <v>3.71</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43787</v>
       </c>
       <c r="K46" t="n">
@@ -9357,13 +9369,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9390,7 +9402,7 @@
       <c r="I47" t="n">
         <v>3.5</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K47" t="n">
@@ -9403,13 +9415,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9436,7 +9448,7 @@
       <c r="I48" t="n">
         <v>3.5</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="K48" t="n">
@@ -9449,13 +9461,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9482,7 +9494,7 @@
       <c r="I49" t="n">
         <v>3.2</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9495,13 +9507,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44151</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9528,7 +9540,7 @@
       <c r="I50" t="n">
         <v>3.24</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44151</v>
       </c>
       <c r="K50" t="n">
@@ -9541,13 +9553,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9574,7 +9586,7 @@
       <c r="I51" t="n">
         <v>3.45</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="K51" t="n">
@@ -9587,13 +9599,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9620,7 +9632,7 @@
       <c r="I52" t="n">
         <v>3.54</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K52" t="n">
@@ -9633,13 +9645,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="I53" t="n">
         <v>3.91</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K53" t="n">
@@ -9679,13 +9691,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44515</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9712,7 +9724,7 @@
       <c r="I54" t="n">
         <v>3.82</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44515</v>
       </c>
       <c r="K54" t="n">
@@ -9725,13 +9737,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9758,7 +9770,7 @@
       <c r="I55" t="n">
         <v>4.58</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="K55" t="n">
@@ -9771,13 +9783,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="I56" t="n">
         <v>4.78</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9817,13 +9829,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9850,7 +9862,7 @@
       <c r="I57" t="n">
         <v>5.28</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="K57" t="n">
@@ -9863,13 +9875,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44879</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9896,7 +9908,7 @@
       <c r="I58" t="n">
         <v>5.41</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44879</v>
       </c>
       <c r="K58" t="n">
@@ -9909,13 +9921,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="I59" t="n">
         <v>7.88</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="K59" t="n">
@@ -9955,13 +9967,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9988,7 +10000,7 @@
       <c r="I60" t="n">
         <v>8.129999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -10001,13 +10013,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10034,7 +10046,7 @@
       <c r="I61" t="n">
         <v>22.87</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -10047,13 +10059,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10080,7 +10092,7 @@
       <c r="I62" t="n">
         <v>22.92</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="K62" t="n">
@@ -10093,13 +10105,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10126,7 +10138,7 @@
       <c r="I63" t="n">
         <v>19.2</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="K63" t="n">
@@ -10139,13 +10151,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10172,7 +10184,7 @@
       <c r="I64" t="n">
         <v>18.69</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K64" t="n">
@@ -10185,13 +10197,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10218,7 +10230,7 @@
       <c r="I65" t="n">
         <v>2.98</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10231,13 +10243,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10264,7 +10276,7 @@
       <c r="I66" t="n">
         <v>3.42</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="K66" t="n">
@@ -10277,13 +10289,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10310,7 +10322,7 @@
       <c r="I67" t="n">
         <v>4.19</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K67" t="n">
@@ -10323,13 +10335,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10356,7 +10368,7 @@
       <c r="I68" t="n">
         <v>4.18</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10369,13 +10381,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10402,7 +10414,7 @@
       <c r="I69" t="n">
         <v>4.65</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K69" t="n">
@@ -10415,13 +10427,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10448,7 +10460,7 @@
       <c r="I70" t="n">
         <v>4.04</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="K70" t="n">
@@ -10461,13 +10473,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10494,7 +10506,7 @@
       <c r="I71" t="n">
         <v>4.09</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="K71" t="n">
@@ -10507,13 +10519,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10540,7 +10552,7 @@
       <c r="I72" t="n">
         <v>4.327690941385436</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K72" t="n">
@@ -10553,13 +10565,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10586,7 +10598,7 @@
       <c r="I73" t="n">
         <v>4.567690941385435</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K73" t="n">
@@ -10623,52 +10635,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10697,10 +10709,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40140</v>
       </c>
       <c r="C3" t="n">
@@ -10729,10 +10741,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40212</v>
       </c>
       <c r="C4" t="n">
@@ -10761,10 +10773,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C5" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C6" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="C7" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40576</v>
       </c>
       <c r="C8" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C9" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="C11" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="C12" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C13" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C14" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="C15" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="C16" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C18" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41597</v>
       </c>
       <c r="C19" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="C20" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C21" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C22" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="C23" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42039</v>
       </c>
       <c r="C24" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42326</v>
       </c>
       <c r="C27" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="C28" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42690</v>
       </c>
       <c r="C31" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="C32" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="C35" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="C36" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C38" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43423</v>
       </c>
       <c r="C39" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="C40" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C41" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C42" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43787</v>
       </c>
       <c r="C43" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C44" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="C45" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44151</v>
       </c>
       <c r="C47" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="C48" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44515</v>
       </c>
       <c r="C51" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="C52" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="C54" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44879</v>
       </c>
       <c r="C55" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="C56" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C57" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="C59" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="C60" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C61" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C62" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="C63" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C64" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C65" t="n">
@@ -12713,10 +12725,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C66" t="n">
@@ -12745,10 +12757,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="C67" t="n">
@@ -12777,10 +12789,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C68" t="n">
@@ -12809,10 +12821,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C69" t="n">
@@ -12841,10 +12853,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C70" t="n">
@@ -12891,12 +12903,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/EMR.xlsx
+++ b/salidas/empresas/EMR.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.1800422668457</v>
+        <v>22.18004608154297</v>
       </c>
       <c r="C2" t="n">
         <v>38.72499847412109</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.5529727935791</v>
+        <v>23.55295562744141</v>
       </c>
       <c r="C3" t="n">
         <v>40.90499877929688</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.07694816589355</v>
+        <v>24.07693672180176</v>
       </c>
       <c r="C4" t="n">
         <v>41.81499862670898</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>23.87897300720215</v>
+        <v>23.87899398803711</v>
       </c>
       <c r="C6" t="n">
         <v>41.2599983215332</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25228500366211</v>
+        <v>24.25228309631348</v>
       </c>
       <c r="C7" t="n">
         <v>41.90499877929688</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>22.83725929260254</v>
+        <v>22.83724594116211</v>
       </c>
       <c r="C8" t="n">
         <v>39.45999908447266</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>23.90591812133789</v>
+        <v>23.90592193603516</v>
       </c>
       <c r="C9" t="n">
         <v>41.07500076293945</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>24.40353584289551</v>
+        <v>24.40353012084961</v>
       </c>
       <c r="C10" t="n">
         <v>41.93000030517578</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>24.56067657470703</v>
+        <v>24.5606746673584</v>
       </c>
       <c r="C11" t="n">
         <v>42.20000076293945</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>25.38201141357422</v>
+        <v>25.38201522827148</v>
       </c>
       <c r="C12" t="n">
         <v>43.34999847412109</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>26.33053779602051</v>
+        <v>26.33053970336914</v>
       </c>
       <c r="C14" t="n">
         <v>44.97000122070312</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.35577774047852</v>
+        <v>25.35577201843262</v>
       </c>
       <c r="C15" t="n">
         <v>43.04999923706055</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>25.37934684753418</v>
+        <v>25.37933158874512</v>
       </c>
       <c r="C16" t="n">
         <v>43.09000015258789</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.67637634277344</v>
+        <v>27.67637062072754</v>
       </c>
       <c r="C17" t="n">
         <v>46.9900016784668</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.69794654846191</v>
+        <v>28.69795036315918</v>
       </c>
       <c r="C18" t="n">
         <v>48.45000076293945</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>27.72061729431152</v>
+        <v>27.72062492370605</v>
       </c>
       <c r="C19" t="n">
         <v>46.79999923706055</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>27.88054084777832</v>
+        <v>27.88055992126465</v>
       </c>
       <c r="C20" t="n">
         <v>47.06999969482422</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>29.32408332824707</v>
+        <v>29.3240852355957</v>
       </c>
       <c r="C21" t="n">
         <v>49.22999954223633</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>31.70075416564941</v>
+        <v>31.70074272155762</v>
       </c>
       <c r="C22" t="n">
         <v>53.22000122070312</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>31.13488578796387</v>
+        <v>31.13486480712891</v>
       </c>
       <c r="C23" t="n">
         <v>52.27000045776367</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>33.93289184570312</v>
+        <v>33.93286895751953</v>
       </c>
       <c r="C25" t="n">
         <v>56.65999984741211</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.41142463684082</v>
+        <v>30.41144371032715</v>
       </c>
       <c r="C26" t="n">
         <v>50.77999877929688</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>30.69809341430664</v>
+        <v>30.69809532165527</v>
       </c>
       <c r="C27" t="n">
         <v>50.95999908447266</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.99930000305176</v>
+        <v>30.99928283691406</v>
       </c>
       <c r="C28" t="n">
         <v>51.45999908447266</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.48121643066406</v>
+        <v>31.48120307922363</v>
       </c>
       <c r="C29" t="n">
         <v>52.2599983215332</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>35.23492050170898</v>
+        <v>35.23490905761719</v>
       </c>
       <c r="C30" t="n">
         <v>58.18000030517578</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>29.94785499572754</v>
+        <v>29.94784927368164</v>
       </c>
       <c r="C31" t="n">
         <v>49.45000076293945</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>29.49364852905273</v>
+        <v>29.4936351776123</v>
       </c>
       <c r="C32" t="n">
         <v>48.70000076293945</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.51703453063965</v>
+        <v>28.51702880859375</v>
       </c>
       <c r="C33" t="n">
         <v>46.79999923706055</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.85491180419922</v>
+        <v>24.85490989685059</v>
       </c>
       <c r="C34" t="n">
         <v>40.79000091552734</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>19.94364547729492</v>
+        <v>19.94364166259766</v>
       </c>
       <c r="C35" t="n">
         <v>32.72999954223633</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>22.09854125976562</v>
+        <v>22.09854507446289</v>
       </c>
       <c r="C36" t="n">
         <v>35.88999938964844</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.5418701171875</v>
+        <v>22.5418815612793</v>
       </c>
       <c r="C37" t="n">
         <v>36.61000061035156</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>20.13437080383301</v>
+        <v>20.13436889648438</v>
       </c>
       <c r="C38" t="n">
         <v>32.70000076293945</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>17.77646446228027</v>
+        <v>17.77646827697754</v>
       </c>
       <c r="C40" t="n">
         <v>28.57999992370605</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.17253112792969</v>
+        <v>21.17251968383789</v>
       </c>
       <c r="C41" t="n">
         <v>34.04000091552734</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.14724349975586</v>
+        <v>20.14724731445312</v>
       </c>
       <c r="C42" t="n">
         <v>32.09000015258789</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>20.34187698364258</v>
+        <v>20.34187889099121</v>
       </c>
       <c r="C43" t="n">
         <v>32.40000152587891</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.84066009521484</v>
+        <v>22.84066581726074</v>
       </c>
       <c r="C44" t="n">
         <v>36.38000106811523</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.39664840698242</v>
+        <v>25.39665603637695</v>
       </c>
       <c r="C46" t="n">
         <v>40.08000183105469</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>23.92024803161621</v>
+        <v>23.92024040222168</v>
       </c>
       <c r="C47" t="n">
         <v>37.75</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>26.45108413696289</v>
+        <v>26.45109748840332</v>
       </c>
       <c r="C48" t="n">
         <v>41.40999984741211</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.21121978759766</v>
+        <v>27.21121597290039</v>
       </c>
       <c r="C49" t="n">
         <v>42.59999847412109</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>26.53413581848145</v>
+        <v>26.53412437438965</v>
       </c>
       <c r="C50" t="n">
         <v>41.54000091552734</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>30.46170425415039</v>
+        <v>30.46170043945312</v>
       </c>
       <c r="C51" t="n">
         <v>47.34000015258789</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.39212036132812</v>
+        <v>32.39210891723633</v>
       </c>
       <c r="C52" t="n">
         <v>50.34000015258789</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>33.60824203491211</v>
+        <v>33.60824966430664</v>
       </c>
       <c r="C53" t="n">
         <v>52.22999954223633</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>30.08454704284668</v>
+        <v>30.08455848693848</v>
       </c>
       <c r="C54" t="n">
         <v>46.43999862670898</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.30305862426758</v>
+        <v>28.30306243896484</v>
       </c>
       <c r="C55" t="n">
         <v>43.68999862670898</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.09278869628906</v>
+        <v>32.0927848815918</v>
       </c>
       <c r="C56" t="n">
         <v>49.54000091552734</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>30.4213981628418</v>
+        <v>30.42141342163086</v>
       </c>
       <c r="C57" t="n">
         <v>46.65000152587891</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>34.34065628051758</v>
+        <v>34.34064865112305</v>
       </c>
       <c r="C58" t="n">
         <v>52.65999984741211</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>35.80139923095703</v>
+        <v>35.8014030456543</v>
       </c>
       <c r="C59" t="n">
         <v>54.90000152587891</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>36.1314811706543</v>
+        <v>36.13148880004883</v>
       </c>
       <c r="C60" t="n">
         <v>55.06999969482422</v>
@@ -1719,7 +1719,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>37.50930786132812</v>
+        <v>37.50930023193359</v>
       </c>
       <c r="C61" t="n">
         <v>57.16999816894531</v>
@@ -1748,7 +1748,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>38.6312370300293</v>
+        <v>38.63124084472656</v>
       </c>
       <c r="C62" t="n">
         <v>58.88000106811523</v>
@@ -1777,7 +1777,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.36442947387695</v>
+        <v>39.36442565917969</v>
       </c>
       <c r="C63" t="n">
         <v>59.65999984741211</v>
@@ -1806,7 +1806,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>38.55286407470703</v>
+        <v>38.5528678894043</v>
       </c>
       <c r="C64" t="n">
         <v>58.43000030517578</v>
@@ -1835,7 +1835,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>40.09682464599609</v>
+        <v>40.09681701660156</v>
       </c>
       <c r="C65" t="n">
         <v>60.77000045776367</v>
@@ -1864,7 +1864,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>36.21845245361328</v>
+        <v>36.21846008300781</v>
       </c>
       <c r="C66" t="n">
         <v>54.54999923706055</v>
@@ -1893,7 +1893,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.34716033935547</v>
+        <v>37.3471794128418</v>
       </c>
       <c r="C67" t="n">
         <v>56.25</v>
@@ -1922,7 +1922,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>32.59329223632812</v>
+        <v>32.59329605102539</v>
       </c>
       <c r="C68" t="n">
         <v>49.09000015258789</v>
@@ -1951,7 +1951,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.14708709716797</v>
+        <v>31.14710998535156</v>
       </c>
       <c r="C69" t="n">
         <v>46.54999923706055</v>
@@ -1980,7 +1980,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>27.64095306396484</v>
+        <v>27.64094924926758</v>
       </c>
       <c r="C70" t="n">
         <v>41.31000137329102</v>
@@ -2009,7 +2009,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.19758987426758</v>
+        <v>32.19760513305664</v>
       </c>
       <c r="C71" t="n">
         <v>48.11999893188477</v>
@@ -2038,7 +2038,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>35.23799514770508</v>
+        <v>35.23800277709961</v>
       </c>
       <c r="C72" t="n">
         <v>52.25</v>
@@ -2067,7 +2067,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>31.42082786560059</v>
+        <v>31.42082977294922</v>
       </c>
       <c r="C73" t="n">
         <v>46.59000015258789</v>
@@ -2096,7 +2096,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>34.65126037597656</v>
+        <v>34.65126419067383</v>
       </c>
       <c r="C74" t="n">
         <v>51.38000106811523</v>
@@ -2154,7 +2154,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.46561813354492</v>
+        <v>35.46560668945312</v>
       </c>
       <c r="C76" t="n">
         <v>52.18000030517578</v>
@@ -2212,7 +2212,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.04933166503906</v>
+        <v>32.04933929443359</v>
       </c>
       <c r="C78" t="n">
         <v>46.77000045776367</v>
@@ -2241,7 +2241,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>31.91912651062012</v>
+        <v>31.91913986206055</v>
       </c>
       <c r="C79" t="n">
         <v>46.58000183105469</v>
@@ -2299,7 +2299,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>35.02650451660156</v>
+        <v>35.02650833129883</v>
       </c>
       <c r="C81" t="n">
         <v>50.72000122070312</v>
@@ -2328,7 +2328,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.33457183837891</v>
+        <v>33.33457565307617</v>
       </c>
       <c r="C82" t="n">
         <v>48.27000045776367</v>
@@ -2357,7 +2357,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>33.44505310058594</v>
+        <v>33.44506454467773</v>
       </c>
       <c r="C83" t="n">
         <v>48.43000030517578</v>
@@ -2386,7 +2386,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>34.97543334960938</v>
+        <v>34.97542953491211</v>
       </c>
       <c r="C84" t="n">
         <v>50.22999954223633</v>
@@ -2444,7 +2444,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>39.86348724365234</v>
+        <v>39.86349487304688</v>
       </c>
       <c r="C86" t="n">
         <v>57.25</v>
@@ -2473,7 +2473,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>39.76120376586914</v>
+        <v>39.76121139526367</v>
       </c>
       <c r="C87" t="n">
         <v>56.70000076293945</v>
@@ -2502,7 +2502,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>39.17917251586914</v>
+        <v>39.17915725708008</v>
       </c>
       <c r="C88" t="n">
         <v>55.86999893188477</v>
@@ -2531,7 +2531,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>38.92671966552734</v>
+        <v>38.92672348022461</v>
       </c>
       <c r="C89" t="n">
         <v>55.5099983215332</v>
@@ -2589,7 +2589,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>38.51414489746094</v>
+        <v>38.51414108276367</v>
       </c>
       <c r="C91" t="n">
         <v>54.54000091552734</v>
@@ -2618,7 +2618,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>43.33723068237305</v>
+        <v>43.33723831176758</v>
       </c>
       <c r="C92" t="n">
         <v>61.36999893188477</v>
@@ -2647,7 +2647,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>42.9129753112793</v>
+        <v>42.91297912597656</v>
       </c>
       <c r="C93" t="n">
         <v>60.36999893188477</v>
@@ -2676,7 +2676,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>45.99089050292969</v>
+        <v>45.99088668823242</v>
       </c>
       <c r="C94" t="n">
         <v>64.69999694824219</v>
@@ -2705,7 +2705,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>47.60446548461914</v>
+        <v>47.60448837280273</v>
       </c>
       <c r="C95" t="n">
         <v>66.97000122070312</v>
@@ -2734,7 +2734,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>47.92956161499023</v>
+        <v>47.92955017089844</v>
       </c>
       <c r="C96" t="n">
         <v>66.98999786376953</v>
@@ -2763,7 +2763,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>50.2119140625</v>
+        <v>50.21192932128906</v>
       </c>
       <c r="C97" t="n">
         <v>70.18000030517578</v>
@@ -2792,7 +2792,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>47.17830276489258</v>
+        <v>47.17831802368164</v>
       </c>
       <c r="C98" t="n">
         <v>65.94000244140625</v>
@@ -2850,7 +2850,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>48.11214828491211</v>
+        <v>48.11213684082031</v>
       </c>
       <c r="C100" t="n">
         <v>66.80000305175781</v>
@@ -2879,7 +2879,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>49.1060791015625</v>
+        <v>49.10608291625977</v>
       </c>
       <c r="C101" t="n">
         <v>68.18000030517578</v>
@@ -2908,7 +2908,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.36631393432617</v>
+        <v>48.36631011962891</v>
       </c>
       <c r="C102" t="n">
         <v>66.73000335693359</v>
@@ -2937,7 +2937,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>48.09814834594727</v>
+        <v>48.09814071655273</v>
       </c>
       <c r="C103" t="n">
         <v>66.36000061035156</v>
@@ -2966,7 +2966,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>46.13391876220703</v>
+        <v>46.1339111328125</v>
       </c>
       <c r="C104" t="n">
         <v>63.65000152587891</v>
@@ -3053,7 +3053,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>46.75186157226562</v>
+        <v>46.75186920166016</v>
       </c>
       <c r="C107" t="n">
         <v>64.05999755859375</v>
@@ -3082,7 +3082,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>46.8668098449707</v>
+        <v>46.86681365966797</v>
       </c>
       <c r="C108" t="n">
         <v>63.75</v>
@@ -3111,7 +3111,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>45.38177871704102</v>
+        <v>45.38177490234375</v>
       </c>
       <c r="C109" t="n">
         <v>61.72999954223633</v>
@@ -3140,7 +3140,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>41.86033630371094</v>
+        <v>41.86032485961914</v>
       </c>
       <c r="C110" t="n">
         <v>56.93999862670898</v>
@@ -3169,7 +3169,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>42.92844009399414</v>
+        <v>42.92842483520508</v>
       </c>
       <c r="C111" t="n">
         <v>57.91999816894531</v>
@@ -3198,7 +3198,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.96491241455078</v>
+        <v>41.96490478515625</v>
       </c>
       <c r="C112" t="n">
         <v>56.61999893188477</v>
@@ -3227,7 +3227,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>43.60288238525391</v>
+        <v>43.6028938293457</v>
       </c>
       <c r="C113" t="n">
         <v>58.83000183105469</v>
@@ -3256,7 +3256,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>45.05166244506836</v>
+        <v>45.05167007446289</v>
       </c>
       <c r="C114" t="n">
         <v>60.31000137329102</v>
@@ -3285,7 +3285,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>41.40629577636719</v>
+        <v>41.40629959106445</v>
       </c>
       <c r="C115" t="n">
         <v>55.43000030517578</v>
@@ -3314,7 +3314,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>38.6573371887207</v>
+        <v>38.65731811523438</v>
       </c>
       <c r="C116" t="n">
         <v>51.75</v>
@@ -3343,7 +3343,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>35.99264907836914</v>
+        <v>35.99264144897461</v>
       </c>
       <c r="C117" t="n">
         <v>47.72000122070312</v>
@@ -3401,7 +3401,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>35.62305450439453</v>
+        <v>35.62306213378906</v>
       </c>
       <c r="C119" t="n">
         <v>47.22999954223633</v>
@@ -3459,7 +3459,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>36.43376922607422</v>
+        <v>36.43378448486328</v>
       </c>
       <c r="C121" t="n">
         <v>47.83000183105469</v>
@@ -3517,7 +3517,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>37.57598495483398</v>
+        <v>37.57599258422852</v>
       </c>
       <c r="C123" t="n">
         <v>48.83000183105469</v>
@@ -3546,7 +3546,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>41.84684753417969</v>
+        <v>41.84685516357422</v>
       </c>
       <c r="C124" t="n">
         <v>54.38000106811523</v>
@@ -3575,7 +3575,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>42.03923797607422</v>
+        <v>42.03924560546875</v>
       </c>
       <c r="C125" t="n">
         <v>54.63000106811523</v>
@@ -3604,7 +3604,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>40.38937377929688</v>
+        <v>40.38936996459961</v>
       </c>
       <c r="C126" t="n">
         <v>52.02000045776367</v>
@@ -3633,7 +3633,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.49808502197266</v>
+        <v>40.49806594848633</v>
       </c>
       <c r="C127" t="n">
         <v>52.15999984741211</v>
@@ -3662,7 +3662,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>43.40188598632812</v>
+        <v>43.40189743041992</v>
       </c>
       <c r="C128" t="n">
         <v>55.90000152587891</v>
@@ -3720,7 +3720,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>42.69595336914062</v>
+        <v>42.69594573974609</v>
       </c>
       <c r="C130" t="n">
         <v>54.5099983215332</v>
@@ -3749,7 +3749,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>39.69602966308594</v>
+        <v>39.69602203369141</v>
       </c>
       <c r="C131" t="n">
         <v>50.68000030517578</v>
@@ -3778,7 +3778,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>44.63281631469727</v>
+        <v>44.63282012939453</v>
       </c>
       <c r="C132" t="n">
         <v>56.43999862670898</v>
@@ -3807,7 +3807,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.0871696472168</v>
+        <v>44.08716201782227</v>
       </c>
       <c r="C133" t="n">
         <v>55.75</v>
@@ -3836,7 +3836,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>46.38839340209961</v>
+        <v>46.38840103149414</v>
       </c>
       <c r="C134" t="n">
         <v>58.65999984741211</v>
@@ -3865,7 +3865,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>47.8855094909668</v>
+        <v>47.885498046875</v>
       </c>
       <c r="C135" t="n">
         <v>60.09999847412109</v>
@@ -3894,7 +3894,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>47.69427108764648</v>
+        <v>47.69427871704102</v>
       </c>
       <c r="C136" t="n">
         <v>59.86000061035156</v>
@@ -3923,7 +3923,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.0289192199707</v>
+        <v>48.02892684936523</v>
       </c>
       <c r="C137" t="n">
         <v>60.27999877929688</v>
@@ -3952,7 +3952,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>47.49203872680664</v>
+        <v>47.49203109741211</v>
       </c>
       <c r="C138" t="n">
         <v>59.11999893188477</v>
@@ -3981,7 +3981,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>47.8936882019043</v>
+        <v>47.89369964599609</v>
       </c>
       <c r="C139" t="n">
         <v>59.61999893188477</v>
@@ -4010,7 +4010,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>47.88566589355469</v>
+        <v>47.88564682006836</v>
       </c>
       <c r="C140" t="n">
         <v>59.61000061035156</v>
@@ -4039,7 +4039,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>47.80751037597656</v>
+        <v>47.80751800537109</v>
       </c>
       <c r="C141" t="n">
         <v>59.04000091552734</v>
@@ -4068,7 +4068,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>50.88454818725586</v>
+        <v>50.88454437255859</v>
       </c>
       <c r="C142" t="n">
         <v>62.84000015258789</v>
@@ -4097,7 +4097,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>52.19633102416992</v>
+        <v>52.19634628295898</v>
       </c>
       <c r="C143" t="n">
         <v>64.45999908447266</v>
@@ -4126,7 +4126,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>52.91856002807617</v>
+        <v>52.91855239868164</v>
       </c>
       <c r="C144" t="n">
         <v>64.81999969482422</v>
@@ -4155,7 +4155,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>56.89437866210938</v>
+        <v>56.89436721801758</v>
       </c>
       <c r="C145" t="n">
         <v>69.69000244140625</v>
@@ -4184,7 +4184,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>58.96801376342773</v>
+        <v>58.96800994873047</v>
       </c>
       <c r="C146" t="n">
         <v>72.23000335693359</v>
@@ -4213,7 +4213,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>58.41011428833008</v>
+        <v>58.41010284423828</v>
       </c>
       <c r="C147" t="n">
         <v>71.05999755859375</v>
@@ -4242,7 +4242,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>56.14143371582031</v>
+        <v>56.14142990112305</v>
       </c>
       <c r="C148" t="n">
         <v>68.30000305175781</v>
@@ -4300,7 +4300,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>58.62452697753906</v>
+        <v>58.62454986572266</v>
       </c>
       <c r="C150" t="n">
         <v>70.83999633789062</v>
@@ -4329,7 +4329,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>57.21768188476562</v>
+        <v>57.21769332885742</v>
       </c>
       <c r="C151" t="n">
         <v>69.13999938964844</v>
@@ -4358,7 +4358,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>59.81624221801758</v>
+        <v>59.81623840332031</v>
       </c>
       <c r="C152" t="n">
         <v>72.27999877929688</v>
@@ -4387,7 +4387,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>63.92035675048828</v>
+        <v>63.92035293579102</v>
       </c>
       <c r="C153" t="n">
         <v>76.73000335693359</v>
@@ -4416,7 +4416,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>63.79540252685547</v>
+        <v>63.7953987121582</v>
       </c>
       <c r="C154" t="n">
         <v>76.58000183105469</v>
@@ -4445,7 +4445,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>56.54779052734375</v>
+        <v>56.54780960083008</v>
       </c>
       <c r="C155" t="n">
         <v>67.87999725341797</v>
@@ -4503,7 +4503,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>50.13959503173828</v>
+        <v>50.13957977294922</v>
       </c>
       <c r="C157" t="n">
         <v>59.75</v>
@@ -4532,7 +4532,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>54.93955230712891</v>
+        <v>54.93954849243164</v>
       </c>
       <c r="C158" t="n">
         <v>65.47000122070312</v>
@@ -4561,7 +4561,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>57.60106658935547</v>
+        <v>57.6010627746582</v>
       </c>
       <c r="C159" t="n">
         <v>68.15000152587891</v>
@@ -4619,7 +4619,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>60.00147247314453</v>
+        <v>60.00146102905273</v>
       </c>
       <c r="C161" t="n">
         <v>70.98999786376953</v>
@@ -4677,7 +4677,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>56.817138671875</v>
+        <v>56.81714248657227</v>
       </c>
       <c r="C163" t="n">
         <v>66.72000122070312</v>
@@ -4706,7 +4706,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>55.25024032592773</v>
+        <v>55.25023651123047</v>
       </c>
       <c r="C164" t="n">
         <v>64.87999725341797</v>
@@ -4735,7 +4735,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>51.18433380126953</v>
+        <v>51.1843376159668</v>
       </c>
       <c r="C165" t="n">
         <v>59.59000015258789</v>
@@ -4764,7 +4764,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>57.4288330078125</v>
+        <v>57.42884063720703</v>
       </c>
       <c r="C166" t="n">
         <v>66.86000061035156</v>
@@ -4822,7 +4822,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>63.87547302246094</v>
+        <v>63.87548446655273</v>
       </c>
       <c r="C168" t="n">
         <v>73.86000061035156</v>
@@ -4880,7 +4880,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>61.94693756103516</v>
+        <v>61.94695281982422</v>
       </c>
       <c r="C170" t="n">
         <v>71.62999725341797</v>
@@ -4938,7 +4938,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>41.48368835449219</v>
+        <v>41.48368072509766</v>
       </c>
       <c r="C172" t="n">
         <v>47.65000152587891</v>
@@ -4967,7 +4967,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>49.64984130859375</v>
+        <v>49.64983749389648</v>
       </c>
       <c r="C173" t="n">
         <v>57.02999877929688</v>
@@ -4996,7 +4996,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>53.6402587890625</v>
+        <v>53.64026260375977</v>
       </c>
       <c r="C174" t="n">
         <v>61.02000045776367</v>
@@ -5054,7 +5054,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>54.51052474975586</v>
+        <v>54.51052856445312</v>
       </c>
       <c r="C176" t="n">
         <v>62.0099983215332</v>
@@ -5083,7 +5083,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>61.49663162231445</v>
+        <v>61.49662780761719</v>
       </c>
       <c r="C177" t="n">
         <v>69.47000122070312</v>
@@ -5112,7 +5112,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>58.04423904418945</v>
+        <v>58.04425048828125</v>
       </c>
       <c r="C178" t="n">
         <v>65.56999969482422</v>
@@ -5141,7 +5141,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>57.3537712097168</v>
+        <v>57.35377502441406</v>
       </c>
       <c r="C179" t="n">
         <v>64.79000091552734</v>
@@ -5170,7 +5170,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>68.46464538574219</v>
+        <v>68.46465301513672</v>
       </c>
       <c r="C180" t="n">
         <v>76.81999969482422</v>
@@ -5199,7 +5199,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>71.62851715087891</v>
+        <v>71.62852478027344</v>
       </c>
       <c r="C181" t="n">
         <v>80.37000274658203</v>
@@ -5257,7 +5257,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>77.01429748535156</v>
+        <v>77.0142822265625</v>
       </c>
       <c r="C183" t="n">
         <v>85.90000152587891</v>
@@ -5286,7 +5286,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>80.88739776611328</v>
+        <v>80.88740539550781</v>
       </c>
       <c r="C184" t="n">
         <v>90.22000122070312</v>
@@ -5315,7 +5315,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>81.12947845458984</v>
+        <v>81.12947082519531</v>
       </c>
       <c r="C185" t="n">
         <v>90.48999786376953</v>
@@ -5344,7 +5344,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>86.25823974609375</v>
+        <v>86.25823211669922</v>
       </c>
       <c r="C186" t="n">
         <v>95.69000244140625</v>
@@ -5373,7 +5373,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>86.75403594970703</v>
+        <v>86.75400543212891</v>
       </c>
       <c r="C187" t="n">
         <v>96.23999786376953</v>
@@ -5402,7 +5402,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>90.94566345214844</v>
+        <v>90.94568634033203</v>
       </c>
       <c r="C188" t="n">
         <v>100.8899993896484</v>
@@ -5431,7 +5431,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>95.5640869140625</v>
+        <v>95.56407928466797</v>
       </c>
       <c r="C189" t="n">
         <v>105.5</v>
@@ -5460,7 +5460,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>85.32831573486328</v>
+        <v>85.32830810546875</v>
       </c>
       <c r="C190" t="n">
         <v>94.19999694824219</v>
@@ -5576,7 +5576,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>83.73249053955078</v>
+        <v>83.73248291015625</v>
       </c>
       <c r="C194" t="n">
         <v>91.94999694824219</v>
@@ -5605,7 +5605,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>85.06090545654297</v>
+        <v>85.06089019775391</v>
       </c>
       <c r="C195" t="n">
         <v>92.91999816894531</v>
@@ -5634,7 +5634,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>89.75701141357422</v>
+        <v>89.75701904296875</v>
       </c>
       <c r="C196" t="n">
         <v>98.05000305175781</v>
@@ -5692,7 +5692,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>81.66715240478516</v>
+        <v>81.66716003417969</v>
       </c>
       <c r="C198" t="n">
         <v>88.66000366210938</v>
@@ -5779,7 +5779,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>75.73851013183594</v>
+        <v>75.73851776123047</v>
       </c>
       <c r="C201" t="n">
         <v>81.73999786376953</v>
@@ -5837,7 +5837,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>80.24168395996094</v>
+        <v>80.24169921875</v>
       </c>
       <c r="C203" t="n">
         <v>86.59999847412109</v>
@@ -5895,7 +5895,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>89.51718139648438</v>
+        <v>89.51719665527344</v>
       </c>
       <c r="C205" t="n">
         <v>96.05999755859375</v>
@@ -5924,7 +5924,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>84.07496643066406</v>
+        <v>84.074951171875</v>
       </c>
       <c r="C206" t="n">
         <v>90.22000122070312</v>
@@ -5953,7 +5953,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>77.54036712646484</v>
+        <v>77.54034423828125</v>
       </c>
       <c r="C207" t="n">
         <v>82.70999908447266</v>
@@ -5982,7 +5982,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>81.69349670410156</v>
+        <v>81.6934814453125</v>
       </c>
       <c r="C208" t="n">
         <v>87.13999938964844</v>
@@ -6011,7 +6011,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>78.05600738525391</v>
+        <v>78.05599975585938</v>
       </c>
       <c r="C209" t="n">
         <v>83.26000213623047</v>
@@ -6069,7 +6069,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>85.27797698974609</v>
+        <v>85.27798461914062</v>
       </c>
       <c r="C211" t="n">
         <v>90.38999938964844</v>
@@ -6098,7 +6098,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>86.18370819091797</v>
+        <v>86.18370056152344</v>
       </c>
       <c r="C212" t="n">
         <v>91.34999847412109</v>
@@ -6127,7 +6127,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>93.19806671142578</v>
+        <v>93.19808197021484</v>
       </c>
       <c r="C213" t="n">
         <v>98.25</v>
@@ -6156,7 +6156,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>91.60446166992188</v>
+        <v>91.60445404052734</v>
       </c>
       <c r="C214" t="n">
         <v>96.56999969482422</v>
@@ -6185,7 +6185,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>84.39524078369141</v>
+        <v>84.39525604248047</v>
       </c>
       <c r="C215" t="n">
         <v>88.97000122070312</v>
@@ -6243,7 +6243,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>92.87717437744141</v>
+        <v>92.87716674804688</v>
       </c>
       <c r="C217" t="n">
         <v>97.33000183105469</v>
@@ -6272,7 +6272,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>87.53337097167969</v>
+        <v>87.53336334228516</v>
       </c>
       <c r="C218" t="n">
         <v>91.73000335693359</v>
@@ -6301,7 +6301,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>102.4679794311523</v>
+        <v>102.4679718017578</v>
       </c>
       <c r="C219" t="n">
         <v>106.8499984741211</v>
@@ -6417,7 +6417,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>106.1274871826172</v>
+        <v>106.1275024414062</v>
       </c>
       <c r="C223" t="n">
         <v>110.1600036621094</v>
@@ -6446,7 +6446,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>112.8230667114258</v>
+        <v>112.8230819702148</v>
       </c>
       <c r="C224" t="n">
         <v>117.1100006103516</v>
@@ -6475,7 +6475,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>102.0457916259766</v>
+        <v>102.0458068847656</v>
       </c>
       <c r="C225" t="n">
         <v>105.3899993896484</v>
@@ -6504,7 +6504,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>105.8995132446289</v>
+        <v>105.8995056152344</v>
       </c>
       <c r="C226" t="n">
         <v>109.370002746582</v>
@@ -6533,7 +6533,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>104.8344039916992</v>
+        <v>104.8344192504883</v>
       </c>
       <c r="C227" t="n">
         <v>108.2699966430664</v>
@@ -6562,7 +6562,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>128.9200744628906</v>
+        <v>128.9200592041016</v>
       </c>
       <c r="C228" t="n">
         <v>132.6000061035156</v>
@@ -6591,7 +6591,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>120.4906616210938</v>
+        <v>120.4906845092773</v>
       </c>
       <c r="C229" t="n">
         <v>123.9300003051758</v>
@@ -6620,7 +6620,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>126.3435821533203</v>
+        <v>126.3435974121094</v>
       </c>
       <c r="C230" t="n">
         <v>129.9499969482422</v>
@@ -6649,7 +6649,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>118.7353973388672</v>
+        <v>118.7353897094727</v>
       </c>
       <c r="C231" t="n">
         <v>121.6100006103516</v>
@@ -6678,7 +6678,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>107.0483322143555</v>
+        <v>107.04833984375</v>
       </c>
       <c r="C232" t="n">
         <v>109.6399993896484</v>
@@ -6794,7 +6794,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>142.697021484375</v>
+        <v>142.6969909667969</v>
       </c>
       <c r="C236" t="n">
         <v>145.5099945068359</v>
@@ -6881,7 +6881,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>137.4117889404297</v>
+        <v>137.4118041992188</v>
       </c>
       <c r="C239" t="n">
         <v>139.5700073242188</v>
@@ -7055,7 +7055,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>139.4019622802734</v>
+        <v>139.4019470214844</v>
       </c>
       <c r="C245" t="n">
         <v>140.4400024414062</v>
